--- a/R8_ver1002_西新変更版.xlsx
+++ b/R8_ver1002_西新変更版.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="165" formatCode="0.0_ "/>
     <numFmt numFmtId="166" formatCode="aaa"/>
   </numFmts>
-  <fonts count="87">
+  <fonts count="89">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -704,6 +704,15 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="HGP教科書体"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="HGP教科書体"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -2786,7 +2795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1541">
+  <cellXfs count="1543">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7358,6 +7367,12 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -10998,7 +11013,7 @@
           <t>中嶋9</t>
         </is>
       </c>
-      <c r="O90" s="1063" t="inlineStr">
+      <c r="O90" s="101" t="inlineStr">
         <is>
           <t>●倉光9</t>
         </is>
@@ -11077,7 +11092,7 @@
           <t>右田5</t>
         </is>
       </c>
-      <c r="O91" s="1064" t="inlineStr">
+      <c r="O91" s="158" t="inlineStr">
         <is>
           <t>●倉光5</t>
         </is>
@@ -11134,7 +11149,7 @@
           <t>2B(S)</t>
         </is>
       </c>
-      <c r="K92" s="1067" t="inlineStr">
+      <c r="K92" s="210" t="inlineStr">
         <is>
           <t>中嶋</t>
         </is>
@@ -11154,7 +11169,7 @@
           <t>右田5</t>
         </is>
       </c>
-      <c r="O92" s="1063" t="inlineStr">
+      <c r="O92" s="101" t="inlineStr">
         <is>
           <t>●倉光5</t>
         </is>
@@ -11233,7 +11248,7 @@
           <t>副島4</t>
         </is>
       </c>
-      <c r="O93" s="1064" t="inlineStr">
+      <c r="O93" s="158" t="inlineStr">
         <is>
           <t>●倉光4</t>
         </is>
@@ -11312,7 +11327,7 @@
           <t>副島4</t>
         </is>
       </c>
-      <c r="O94" s="1065" t="inlineStr">
+      <c r="O94" s="140" t="inlineStr">
         <is>
           <t>●倉光4</t>
         </is>
@@ -11511,7 +11526,7 @@
           <t>6通</t>
         </is>
       </c>
-      <c r="K97" s="1068" t="inlineStr">
+      <c r="K97" s="204" t="inlineStr">
         <is>
           <t>髙本</t>
         </is>
@@ -11531,7 +11546,7 @@
           <t>中嶋3</t>
         </is>
       </c>
-      <c r="O97" s="1066" t="inlineStr">
+      <c r="O97" s="105" t="inlineStr">
         <is>
           <t>●神田3</t>
         </is>
@@ -11605,7 +11620,7 @@
           <t>副島3</t>
         </is>
       </c>
-      <c r="O98" s="1066" t="inlineStr">
+      <c r="O98" s="105" t="inlineStr">
         <is>
           <t>●神田3</t>
         </is>
@@ -11989,7 +12004,7 @@
           <t>岡野</t>
         </is>
       </c>
-      <c r="I108" s="1428" t="n">
+      <c r="I108" s="1541" t="n">
         <v>51</v>
       </c>
       <c r="J108" s="114" t="n"/>
@@ -12036,7 +12051,7 @@
           <t>黒岩</t>
         </is>
       </c>
-      <c r="F109" s="1428" t="n">
+      <c r="F109" s="1541" t="n">
         <v>50</v>
       </c>
       <c r="G109" s="1422" t="n"/>
@@ -12101,7 +12116,7 @@
           <t>長本</t>
         </is>
       </c>
-      <c r="I110" s="1428" t="n">
+      <c r="I110" s="1541" t="n">
         <v>6</v>
       </c>
       <c r="J110" s="114" t="inlineStr">
@@ -12156,7 +12171,7 @@
           <t>平井</t>
         </is>
       </c>
-      <c r="F111" s="1428" t="n">
+      <c r="F111" s="1541" t="n">
         <v>57</v>
       </c>
       <c r="G111" s="1422" t="n"/>
@@ -12237,22 +12252,22 @@
           <t>国27</t>
         </is>
       </c>
-      <c r="K112" s="1423" t="inlineStr">
+      <c r="K112" s="115" t="inlineStr">
         <is>
           <t>倉光</t>
         </is>
       </c>
-      <c r="L112" s="1424" t="n">
+      <c r="L112" s="1421" t="n">
         <v>27</v>
       </c>
-      <c r="M112" s="1425" t="n"/>
+      <c r="M112" s="1422" t="n"/>
       <c r="N112" s="1426" t="n"/>
       <c r="O112" s="1421" t="n"/>
       <c r="P112" s="1421" t="n"/>
       <c r="Q112" s="927" t="n"/>
     </row>
     <row r="113" ht="20.25" customFormat="1" customHeight="1" s="124">
-      <c r="B113" s="670" t="n"/>
+      <c r="B113" s="1542" t="n"/>
       <c r="C113" s="1421" t="n"/>
       <c r="D113" s="1422" t="n"/>
       <c r="E113" s="935" t="inlineStr">
@@ -12495,676 +12510,676 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>教員</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>教科</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>内訳（セル：コマ数）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>馬渡</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>L89:8 + L90:8 + L93:4 + L94:4 + L96:9 + L98:3</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>日高</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>D77:9 + L77:11 + L78:9 + L79:4 + L80:3 + L81:3 + L82:3</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>副島</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>D91:5 + L91:5 + D92:5 + L92:5 + L97:4 + L99:3</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>佐藤</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>D89:8 + D90:8 + D93:4 + D94:4 + D96:9 + D99:3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>長本</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>D78:8 + D79:8 + D80:5 + D81:5 + D82:5 + D83:4 + D84:4</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>右田</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>国</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>D97:4 + D98:3</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>髙本</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>M89:12 + M91:7 + M93:6 + M96:13</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>小野</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>37</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>E89:12 + E96:13 + E97:5 + E98:4 + E99:3</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>黒岩</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>E77:14 + M77:17 + E80:7 + E81:6 + E82:6</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>伊地知</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>43</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>M90:12 + M92:6 + M94:5 + M97:5 + M98:4 + P98:5 + M99:3 + P99:3</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>平井</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>57</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>E78:12 + M78:13 + E79:12 + M79:5 + P80:5 + M81:4 + E83:6</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>古賀</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>M80:4 + E90:12 + E91:7 + E92:6 + E93:6 + E94:5 + H98:5 + H99:3</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>平野</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>数</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>M82:3 + P82:3 + E84:5</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>藤田</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>F77:9 + N77:12</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>岡野</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="0" t="n">
         <v>51</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>F78:9 + N78:10 + F79:9 + F80:5 + N80:3 + F81:5 + F82:5 + M83:5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>右田</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>F83:4 + F84:4 + N89:9 + N91:5 + N92:5</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>長本</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>N79:3 + N81:3</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>山内</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="0" t="n">
         <v>47</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>F89:9 + F90:9 + F93:4 + F94:4 + F96:10 + F97:3 + F98:3 + E100:5</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>副島</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>N93:4 + N94:4 + N98:3</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>佐藤</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>F91:5 + F92:5</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>中嶋</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>社</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>N90:9 + N96:10 + N97:3 + M100:5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>神田</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>理</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>G89:9 + G90:9 + G93:4 + G94:4 + G96:10 + O97:3 + O98:3 + G100:4</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>田代</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>理</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="0" t="n">
         <v>39</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>O89:9 + G91:5 + G92:5 + O96:10 + G97:3 + G98:3 + O100:4</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>和久</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>理</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>G77:9 + O77:12 + G80:5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>大山</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>理</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>G79:9 + O80:3 + G81:5 + G82:5 + G83:4 + G84:4</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>平野</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>理</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>G78:9 + O78:10 + O79:3 + O81:3 + O83:4</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>倉光</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>理</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>O90:9 + O91:5 + O92:5 + O93:4 + O94:4</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>英</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>H89:10 + H90:10 + H91:7 + H93:8 + H94:5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>中嶋</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>英</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>P89:10 + P90:10 + P91:7 + P92:6 + P94:5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>土井下</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>英</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>H77:13 + H78:10 + H80:7 + H83:8</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>原</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>英</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>H79:10 + H81:6 + H82:6 + H84:5</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>大山</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>英</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>H92:6 + P93:8</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>※シート「R8表紙プランA」の「３．担当者」表を集計。担任列は含めない。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>※高校：原5?(D85)、古賀5?(D101)、髙本・北原5?(L101) は「他教科」欄に高5?として記載（未確定）</t>
         </is>
